--- a/Simulation_studies/cir_parameter_comparison_Xdim2.xlsx
+++ b/Simulation_studies/cir_parameter_comparison_Xdim2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.55637903260983</v>
+        <v>1.792445342185811e-05</v>
       </c>
       <c r="C2" t="n">
         <v>0.5450817913145818</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01129724129524823</v>
+        <v>0.5450638668611599</v>
       </c>
       <c r="E2" t="n">
-        <v>2.07257726734964</v>
+        <v>99.99671160297272</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6377961766522927</v>
+        <v>0.6295831446367834</v>
       </c>
       <c r="C3" t="n">
         <v>0.5938547655757322</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04394141107656047</v>
+        <v>0.0357283790610512</v>
       </c>
       <c r="E3" t="n">
-        <v>7.399353111860609</v>
+        <v>6.016349641719745</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01824107477955189</v>
+        <v>0.5036173530585083</v>
       </c>
       <c r="C4" t="n">
         <v>0.0124333933545323</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005807681425019593</v>
+        <v>0.491183959703976</v>
       </c>
       <c r="E4" t="n">
-        <v>46.7103489724512</v>
+        <v>3950.52215994539</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04999364893232866</v>
+        <v>0.1033797330328833</v>
       </c>
       <c r="C5" t="n">
         <v>0.05559015057568738</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005596501643358717</v>
+        <v>0.0477895824571959</v>
       </c>
       <c r="E5" t="n">
-        <v>10.06743386265691</v>
+        <v>85.96771543572129</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.139638986097883</v>
+        <v>0.7609539008946413</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07887393787074751</v>
+        <v>0.1119748681131919</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06076504822713549</v>
+        <v>0.6489790327814494</v>
       </c>
       <c r="E6" t="n">
-        <v>77.0407182239494</v>
+        <v>579.5756170263282</v>
       </c>
     </row>
     <row r="7">
@@ -557,111 +557,73 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06206019134593488</v>
+        <v>0.3693657949527629</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07644290486368606</v>
+        <v>0.1059701059804418</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01438271351775118</v>
+        <v>0.2633956889723211</v>
       </c>
       <c r="E7" t="n">
-        <v>18.81497510252732</v>
+        <v>248.556596726377</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>kappa_p1</t>
+          <t>lambda1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0530931394238478</v>
+        <v>0.02531112445337835</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6450817913145818</v>
+        <v>0.352759752057376</v>
       </c>
       <c r="D8" t="n">
-        <v>0.591988651890734</v>
+        <v>0.3274486276039976</v>
       </c>
       <c r="E8" t="n">
-        <v>91.7695492046595</v>
+        <v>92.82482644186076</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kappa_p2</t>
+          <t>lambda2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8722777460490261</v>
+        <v>2.96012599854123e-06</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6938547655757322</v>
+        <v>0.1597769708385401</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1784229804732939</v>
+        <v>0.1597740107125416</v>
       </c>
       <c r="E9" t="n">
-        <v>25.71474454387379</v>
+        <v>99.99814733876666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>theta_p1</t>
+          <t>sigma_err</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3509077016172114</v>
+        <v>0.01993599323705686</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0224333933545323</v>
+        <v>0.005798495327151224</v>
       </c>
       <c r="D10" t="n">
-        <v>0.328474308262679</v>
+        <v>0.01413749790990564</v>
       </c>
       <c r="E10" t="n">
-        <v>1464.220339168244</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>theta_p2</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.03572307294603616</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.06559015057568737</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.02986707762965121</v>
-      </c>
-      <c r="E11" t="n">
-        <v>45.53591868215987</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sigma_err</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.37380250836705e-05</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.004307391579211622</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.004293653554127952</v>
-      </c>
-      <c r="E12" t="n">
-        <v>99.6810592946791</v>
+        <v>243.8132155372681</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/cir_parameter_comparison_Xdim2.xlsx
+++ b/Simulation_studies/cir_parameter_comparison_Xdim2.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.792445342185811e-05</v>
+        <v>0.3066009491672954</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5450817913145818</v>
+        <v>0.3107473177365188</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5450638668611599</v>
+        <v>0.004146368569223402</v>
       </c>
       <c r="E2" t="n">
-        <v>99.99671160297272</v>
+        <v>1.334321595895186</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6295831446367834</v>
+        <v>0.7813870614699893</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5938547655757322</v>
+        <v>0.7823380276949019</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0357283790610512</v>
+        <v>0.0009509662249126416</v>
       </c>
       <c r="E3" t="n">
-        <v>6.016349641719745</v>
+        <v>0.1215543909727346</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5036173530585083</v>
+        <v>0.08513989893943773</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0124333933545323</v>
+        <v>0.04856328758271793</v>
       </c>
       <c r="D4" t="n">
-        <v>0.491183959703976</v>
+        <v>0.03657661135671979</v>
       </c>
       <c r="E4" t="n">
-        <v>3950.52215994539</v>
+        <v>75.31741193266372</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1033797330328833</v>
+        <v>0.01870314205731021</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05559015057568738</v>
+        <v>0.0526043510334744</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0477895824571959</v>
+        <v>0.03390120897616419</v>
       </c>
       <c r="E5" t="n">
-        <v>85.96771543572129</v>
+        <v>64.4456367394237</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7609539008946413</v>
+        <v>0.1434384692344346</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1119748681131919</v>
+        <v>0.1396185721603196</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6489790327814494</v>
+        <v>0.003819897074114981</v>
       </c>
       <c r="E6" t="n">
-        <v>579.5756170263282</v>
+        <v>2.735951969003604</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3693657949527629</v>
+        <v>0.1643370988874669</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1059701059804418</v>
+        <v>0.1603302414597809</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2633956889723211</v>
+        <v>0.004006857427686</v>
       </c>
       <c r="E7" t="n">
-        <v>248.556596726377</v>
+        <v>2.499127669991769</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02531112445337835</v>
+        <v>0.1186561396836287</v>
       </c>
       <c r="C8" t="n">
-        <v>0.352759752057376</v>
+        <v>0.1193525188337721</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3274486276039976</v>
+        <v>0.0006963791501433947</v>
       </c>
       <c r="E8" t="n">
-        <v>92.82482644186076</v>
+        <v>0.5834641421462374</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.96012599854123e-06</v>
+        <v>0.6339878198594526</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1597769708385401</v>
+        <v>0.6183032317110568</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1597740107125416</v>
+        <v>0.01568458814839579</v>
       </c>
       <c r="E9" t="n">
-        <v>99.99814733876666</v>
+        <v>2.536714567218283</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01993599323705686</v>
+        <v>0.0001287179442749472</v>
       </c>
       <c r="C10" t="n">
-        <v>0.005798495327151224</v>
+        <v>0.0009947816779470365</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01413749790990564</v>
+        <v>0.0008660637336720894</v>
       </c>
       <c r="E10" t="n">
-        <v>243.8132155372681</v>
+        <v>87.06068405475796</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/cir_parameter_comparison_Xdim2.xlsx
+++ b/Simulation_studies/cir_parameter_comparison_Xdim2.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3066009491672954</v>
+        <v>0.3630239292209826</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3107473177365188</v>
+        <v>0.7810834903898229</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004146368569223402</v>
+        <v>0.4180595611688403</v>
       </c>
       <c r="E2" t="n">
-        <v>1.334321595895186</v>
+        <v>53.52303131643396</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7813870614699893</v>
+        <v>0.1997358334718121</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7823380276949019</v>
+        <v>0.5025577319423724</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009509662249126416</v>
+        <v>0.3028218984705603</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1215543909727346</v>
+        <v>60.25614157803555</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.08513989893943773</v>
+        <v>0.4436534445837668</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04856328758271793</v>
+        <v>0.2222323189350686</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03657661135671979</v>
+        <v>0.2214211256486983</v>
       </c>
       <c r="E4" t="n">
-        <v>75.31741193266372</v>
+        <v>99.63497960591083</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01870314205731021</v>
+        <v>1.339075927337073</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0526043510334744</v>
+        <v>0.3142462885412678</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03390120897616419</v>
+        <v>1.024829638795805</v>
       </c>
       <c r="E5" t="n">
-        <v>64.4456367394237</v>
+        <v>326.123068486526</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1434384692344346</v>
+        <v>0.9752157695723137</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1396185721603196</v>
+        <v>0.4426099114773284</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003819897074114981</v>
+        <v>0.5326058580949853</v>
       </c>
       <c r="E6" t="n">
-        <v>2.735951969003604</v>
+        <v>120.3330165646927</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1643370988874669</v>
+        <v>0.7313071047282373</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1603302414597809</v>
+        <v>0.371005862329404</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004006857427686</v>
+        <v>0.3603012423988334</v>
       </c>
       <c r="E7" t="n">
-        <v>2.499127669991769</v>
+        <v>97.11470329246002</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1186561396836287</v>
+        <v>-0.6974581021872336</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1193525188337721</v>
+        <v>-0.5453229884237274</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0006963791501433947</v>
+        <v>0.1521351137635062</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5834641421462374</v>
+        <v>-27.89816622315104</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6339878198594526</v>
+        <v>-0.3865806668068338</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6183032317110568</v>
+        <v>0.1973165307851206</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01568458814839579</v>
+        <v>0.5838971975919545</v>
       </c>
       <c r="E9" t="n">
-        <v>2.536714567218283</v>
+        <v>295.9190470603923</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0001287179442749472</v>
+        <v>0.0002791942778386423</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009947816779470365</v>
+        <v>0.0002819047686582375</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0008660637336720894</v>
+        <v>2.710490819595205e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>87.06068405475796</v>
+        <v>0.9614916528358636</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/cir_parameter_comparison_Xdim2.xlsx
+++ b/Simulation_studies/cir_parameter_comparison_Xdim2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,10 +446,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Log_like</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Abs Error</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Rel Error (%)</t>
         </is>
@@ -462,16 +472,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3630239292209826</v>
+        <v>0.4972171334987842</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7810834903898229</v>
+        <v>0.5128314427850377</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4180595611688403</v>
+        <v>0.01037506537405945</v>
       </c>
       <c r="E2" t="n">
-        <v>53.52303131643396</v>
+        <v>27070.8195437778</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01561430928625346</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.044725417274867</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +497,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1997358334718121</v>
+        <v>0.5753763338981397</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5025577319423724</v>
+        <v>0.5623051082037978</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3028218984705603</v>
+        <v>0.01869435017827824</v>
       </c>
       <c r="E3" t="n">
-        <v>60.25614157803555</v>
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.01307122569434194</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.3245788636166</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +522,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4436534445837668</v>
+        <v>0.1898921886099832</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2222323189350686</v>
+        <v>0.1936673009556791</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2214211256486983</v>
+        <v>0.002891302269356927</v>
       </c>
       <c r="E4" t="n">
-        <v>99.63497960591083</v>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.003775112345695858</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.949277098956316</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +547,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.339075927337073</v>
+        <v>0.09486800743328255</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3142462885412678</v>
+        <v>0.08926669759242474</v>
       </c>
       <c r="D5" t="n">
-        <v>1.024829638795805</v>
+        <v>0.002344608479018786</v>
       </c>
       <c r="E5" t="n">
-        <v>326.123068486526</v>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005601309840857813</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.274803473107474</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +572,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9752157695723137</v>
+        <v>0.1286253149801341</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4426099114773284</v>
+        <v>0.1261998131599436</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5326058580949853</v>
+        <v>0.003117648836613943</v>
       </c>
       <c r="E6" t="n">
-        <v>120.3330165646927</v>
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.002425501820190495</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.921953574619365</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +597,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7313071047282373</v>
+        <v>0.263761499142499</v>
       </c>
       <c r="C7" t="n">
-        <v>0.371005862329404</v>
+        <v>0.239045938609484</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3603012423988334</v>
+        <v>0.01400099286942716</v>
       </c>
       <c r="E7" t="n">
-        <v>97.11470329246002</v>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.02471556053301505</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10.33925139108574</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +622,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.6974581021872336</v>
+        <v>-0.1097572086442593</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.5453229884237274</v>
+        <v>-0.2000767203856051</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1521351137635062</v>
+        <v>0.1183120465918051</v>
       </c>
       <c r="E8" t="n">
-        <v>-27.89816622315104</v>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.09031951174134578</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-45.14243914398149</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +647,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.3865806668068338</v>
+        <v>-0.7372700536923678</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1973165307851206</v>
+        <v>-0.7015430437775323</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5838971975919545</v>
+        <v>0.4164006061431864</v>
       </c>
       <c r="E9" t="n">
-        <v>295.9190470603923</v>
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.03572700991483546</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-5.092632623432429</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +672,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0002791942778386423</v>
+        <v>0.0005941977624202243</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0002819047686582375</v>
+        <v>0.0005965045990580927</v>
       </c>
       <c r="D10" t="n">
-        <v>2.710490819595205e-06</v>
+        <v>7.717495435956819e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9614916528358636</v>
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.306836637868456e-06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3867257086552314</v>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/cir_parameter_comparison_Xdim2.xlsx
+++ b/Simulation_studies/cir_parameter_comparison_Xdim2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25ec18ff9d9d96f3/KU^J MAT-OEK/Kandidat/Thesis/Thesis_linear_CDS/Simulation_studies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_085D6EBF907BE40F6235547658E49E7F899586D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17829F63-0501-43D8-9F93-A90E67604698}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_085D769F53547C0E62355476586CD6BBBBA386D9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A57BB061-7BD3-4296-9E98-18AFF78845CA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,6 +25,9 @@
     <t>Parameter</t>
   </si>
   <si>
+    <t>True</t>
+  </si>
+  <si>
     <t>SE</t>
   </si>
   <si>
@@ -65,9 +68,6 @@
   </si>
   <si>
     <t>LogLike</t>
-  </si>
-  <si>
-    <t>True</t>
   </si>
 </sst>
 </file>
@@ -144,10 +144,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -443,229 +439,229 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>1.1699609099376791</v>
+        <v>1.0200237736084099</v>
       </c>
       <c r="C2">
-        <v>1.1863557545576069</v>
+        <v>1.072839344173294</v>
       </c>
       <c r="D2">
-        <v>3.2704286297764527E-2</v>
+        <v>7.7297366671076157E-3</v>
       </c>
       <c r="E2">
-        <v>26637.89445822559</v>
+        <v>25284.536098217031</v>
       </c>
       <c r="F2">
-        <v>1.6394844619927799E-2</v>
+        <v>5.2815570564884062E-2</v>
       </c>
       <c r="G2">
-        <v>1.3819501070352589</v>
+        <v>4.9229710722049029</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>1.302526530165546</v>
+        <v>1.812999106272984</v>
       </c>
       <c r="C3">
-        <v>1.32653113991076</v>
+        <v>1.843437656927255</v>
       </c>
       <c r="D3">
-        <v>3.3626276953572017E-2</v>
+        <v>0.13279841932385039</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>2.400460974521379E-2</v>
+        <v>3.0438550654271031E-2</v>
       </c>
       <c r="G3">
-        <v>1.8095775532889979</v>
+        <v>1.651184163450784</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>0.41852698315564157</v>
+        <v>0.78119162892030825</v>
       </c>
       <c r="C4">
-        <v>0.52384761759002851</v>
+        <v>0.30107623134617811</v>
       </c>
       <c r="D4">
-        <v>1.351591164077522E-2</v>
+        <v>3.6025666436460661E-4</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.1053206344343869</v>
+        <v>0.48011539757413019</v>
       </c>
       <c r="G4">
-        <v>20.105204433097661</v>
+        <v>159.46639009908839</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>0.35669905536269919</v>
+        <v>0.29994835889411381</v>
       </c>
       <c r="C5">
-        <v>0.28292314829021092</v>
+        <v>0.77770920795026666</v>
       </c>
       <c r="D5">
-        <v>9.9117816840889241E-3</v>
+        <v>2.277639656064801E-4</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>7.3775907072488323E-2</v>
+        <v>0.4777608490561529</v>
       </c>
       <c r="G5">
-        <v>26.076306416897371</v>
+        <v>61.431810781222623</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>0.31505417728028018</v>
+        <v>0.17889253915978359</v>
       </c>
       <c r="C6">
-        <v>0.3146057205252874</v>
+        <v>0.18229554623582939</v>
       </c>
       <c r="D6">
-        <v>8.1302495122353088E-3</v>
+        <v>4.1502235816488027E-3</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>4.4845675499277649E-4</v>
+        <v>3.403007076045822E-3</v>
       </c>
       <c r="G6">
-        <v>0.14254564546506091</v>
+        <v>1.866752724525409</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7">
-        <v>0.76428982732891859</v>
+        <v>6.6759828343882444E-2</v>
       </c>
       <c r="C7">
-        <v>0.65322025805927142</v>
+        <v>0.11384620950415961</v>
       </c>
       <c r="D7">
-        <v>2.4036063217350662E-2</v>
+        <v>9.4205837105302108E-3</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0.1110695692696472</v>
+        <v>4.7086381160277198E-2</v>
       </c>
       <c r="G7">
-        <v>17.003387126975628</v>
+        <v>41.359638907043973</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>-0.16951786170906899</v>
+        <v>-0.34221316757648979</v>
       </c>
       <c r="C8">
-        <v>0.15605533843867489</v>
+        <v>-0.24767234817781089</v>
       </c>
       <c r="D8">
-        <v>0.31229381540707563</v>
+        <v>0.13777589885468761</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0.32557320014774388</v>
+        <v>9.4540819398678866E-2</v>
       </c>
       <c r="G8">
-        <v>208.62676240690379</v>
+        <v>-38.171729744656581</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>-0.80578443329364569</v>
+        <v>0.1028793562147375</v>
       </c>
       <c r="C9">
-        <v>-0.55554814553933118</v>
+        <v>9.9957223829649111E-2</v>
       </c>
       <c r="D9">
-        <v>0.52042332067976427</v>
+        <v>4.2578837140423299E-2</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0.2502362877543145</v>
+        <v>2.9221323850884E-3</v>
       </c>
       <c r="G9">
-        <v>-45.043132582394428</v>
+        <v>2.923382896336145</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>6.0810556638212507E-4</v>
+        <v>8.3051705456309635E-4</v>
       </c>
       <c r="C10">
-        <v>5.9650459905809272E-4</v>
+        <v>8.2897519808733931E-4</v>
       </c>
       <c r="D10">
-        <v>8.2077732025277943E-6</v>
+        <v>9.8202616308698662E-6</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>1.160096732403235E-5</v>
+        <v>1.5418564757570469E-6</v>
       </c>
       <c r="G10">
-        <v>1.944824456064681</v>
+        <v>0.18599548928779891</v>
       </c>
     </row>
   </sheetData>
